--- a/gd/excel/Item.xlsx
+++ b/gd/excel/Item.xlsx
@@ -764,51 +764,187 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Id
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF8A5A00"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Name
-string</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Name
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Price
-float</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Price
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>float</t>
+          </r>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Rarity
-ItemRarity</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Rarity
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ItemRarity</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>ItemTypeId
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">ItemTypeId
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>DropRange
-ItemDropRange</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">DropRange
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF2F6B4A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ItemDropRange</t>
+          </r>
         </is>
       </c>
       <c r="G2" s="16" t="n"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Tags
-vector&lt;int32&gt;</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Tags
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;int32&gt;</t>
+          </r>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>IsActive
-bool</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">IsActive
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>bool</t>
+          </r>
         </is>
       </c>
     </row>
@@ -839,14 +975,48 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Min
-ItemDropRange</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Min
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ItemDropRange</t>
+          </r>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Max
-ItemDropRange</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Max
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ItemDropRange</t>
+          </r>
         </is>
       </c>
       <c r="H4" s="14" t="n"/>
@@ -1016,8 +1186,9 @@
     <dataValidation sqref="D5:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"common,rare,epic"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="引用" prompt="目标：ItemType.Id；最终以 canonical 校验为准" type="custom">
-      <formula1>TRUE</formula1>
+    <dataValidation sqref="E5:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation sqref="F5:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>-2147483648</formula1>
